--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="503">
   <si>
     <t>Filename</t>
   </si>
@@ -808,715 +808,721 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7637,0.0013,0.1358,0.0276</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0006,0.9997</t>
-  </si>
-  <si>
-    <t>0.9852,0.0001,0.0001,0.0073</t>
-  </si>
-  <si>
-    <t>0.0056,0.0000,0.0000,0.9992</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9695,0.0031,0.0084,0.0050</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0014,0.9995</t>
+  </si>
+  <si>
+    <t>0.9824,0.0001,0.0002,0.0102</t>
+  </si>
+  <si>
+    <t>0.0673,0.0002,0.0001,0.9840</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9773,0.0003,0.0293,0.0000</t>
-  </si>
-  <si>
-    <t>0.0108,0.0009,0.9915,0.0003</t>
-  </si>
-  <si>
-    <t>0.2112,0.0004,0.8816,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9224,0.0006,0.0921,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
+    <t>0.9944,0.0002,0.0037,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.9697,0.0008,0.0298,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0011,0.9961,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0049,0.9951,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9652,0.0011,0.0253,0.0006</t>
-  </si>
-  <si>
-    <t>0.0062,0.0042,0.9902,0.0008</t>
-  </si>
-  <si>
-    <t>0.0070,0.0009,0.9941,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0005,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0519,0.0001,0.9568,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.8364,0.1102,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.5474,0.0332,0.1960,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0011</t>
-  </si>
-  <si>
-    <t>0.0057,0.9894,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.7864,0.0015,0.1547,0.0007</t>
-  </si>
-  <si>
-    <t>0.9477,0.0020,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.1859,0.8529,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.8147,0.3717,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0015,0.9964,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0172,0.9938,0.0005</t>
-  </si>
-  <si>
-    <t>0.0124,0.0001,0.9846,0.0009</t>
-  </si>
-  <si>
-    <t>0.0202,0.0076,0.9815,0.0002</t>
+    <t>0.0020,0.9970,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9128,0.0039,0.0627,0.0011</t>
+  </si>
+  <si>
+    <t>0.9915,0.0002,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0002,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0177,0.0013,0.9835,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.0001,0.9937,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4144,0.6179,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9531,0.0074,0.0178,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0014</t>
+  </si>
+  <si>
+    <t>0.0045,0.9571,0.0613,0.0000</t>
+  </si>
+  <si>
+    <t>0.8982,0.0002,0.0930,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0472,0.9536,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.8881,0.0818,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0146,0.9912,0.0010</t>
+  </si>
+  <si>
+    <t>0.0043,0.0002,0.9935,0.0009</t>
+  </si>
+  <si>
+    <t>0.0100,0.0109,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9803,0.0004,0.8894</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0068,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3116,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0010,0.9950,0.0029</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9982,0.0006</t>
+  </si>
+  <si>
+    <t>0.9943,0.0047,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0012,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9638,0.0335,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9676,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9876,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9990,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6045,0.0011,0.4982,0.0003</t>
+  </si>
+  <si>
+    <t>0.9118,0.0045,0.0679,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9899,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9850,0.9584,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.7489,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0000,0.0030,0.9968</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0017,0.0030,0.0005,0.9985</t>
+  </si>
+  <si>
+    <t>0.0048,0.0012,0.0002,0.9974</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0011,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9807,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9861,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9897,0.0777,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9798,0.9511,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9205,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0040,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0013,0.9937,0.0009</t>
+  </si>
+  <si>
+    <t>0.9957,0.0001,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0034,0.0003</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0017,0.2440,0.0001,0.9447</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0091,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1680,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0004,0.9952,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.0002,0.9926,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0080,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0007,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9851,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0012,0.9985,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9989,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9234,0.0003,0.1087,0.0004</t>
-  </si>
-  <si>
-    <t>0.7683,0.0023,0.2288,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9911,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9931,0.3748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9915,0.3137,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0004,0.0100,0.9938</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.0028,0.9981</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0021,0.9986</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0005,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9043,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9385,0.9812,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9866,0.2422,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9921,0.9683,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8631,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0010,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0016,0.0001,0.0000</t>
+    <t>0.0001,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.1012,0.9072,0.0054,0.0004</t>
+  </si>
+  <si>
+    <t>0.9496,0.0023,0.0393,0.0014</t>
+  </si>
+  <si>
+    <t>0.7126,0.0001,0.3936,0.0003</t>
+  </si>
+  <si>
+    <t>0.5841,0.0289,0.2165,0.0014</t>
+  </si>
+  <si>
+    <t>0.0506,0.0111,0.8724,0.0015</t>
+  </si>
+  <si>
+    <t>0.0125,0.0105,0.0056,0.9836</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.9602,0.0298,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.5917,0.4298,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0000,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.5650,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0250,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0055,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0021,0.9932,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8086,0.0024,0.1954,0.0008</t>
+  </si>
+  <si>
+    <t>0.0074,0.0002,0.9917,0.0010</t>
+  </si>
+  <si>
+    <t>0.9214,0.0036,0.0666,0.0016</t>
+  </si>
+  <si>
+    <t>0.0346,0.0001,0.0001,0.9863</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0017,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.4428,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9980,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9910,0.0005,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.4156,0.7039,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0000,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.1573,0.0000,0.0004,0.9755</t>
+  </si>
+  <si>
+    <t>0.0001,0.0039,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.7168,0.0000,0.0020,0.3270</t>
+  </si>
+  <si>
+    <t>0.9198,0.0004,0.0250,0.0270</t>
+  </si>
+  <si>
+    <t>0.2128,0.7772,0.0075,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.1644,0.8313,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.6159,0.1405,0.0487,0.0075</t>
+  </si>
+  <si>
+    <t>0.9889,0.0040,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.6076,0.4886,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7996,0.2488,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.1841,0.8598,0.0075,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0024,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.6247,0.4469,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9779,0.0081,0.0059,0.0021</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9489,0.0030,0.0347,0.0042</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0086,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0496,0.0092,0.9253,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0116,0.0021,0.9797,0.0030</t>
+  </si>
+  <si>
+    <t>0.0024,0.0004,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.5913,0.0035,0.3370,0.0056</t>
+  </si>
+  <si>
+    <t>0.1074,0.0148,0.8118,0.0007</t>
+  </si>
+  <si>
+    <t>0.2904,0.0688,0.3340,0.0002</t>
+  </si>
+  <si>
+    <t>0.2888,0.0023,0.7132,0.0001</t>
+  </si>
+  <si>
+    <t>0.7755,0.0042,0.1572,0.0045</t>
+  </si>
+  <si>
+    <t>0.4604,0.0029,0.5389,0.0042</t>
+  </si>
+  <si>
+    <t>0.0303,0.9723,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0595,0.9612,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0119,0.9855,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0047,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2245,0.8013,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.9533,0.0135,0.0081,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9778,0.0023,0.0029,0.0016</t>
+  </si>
+  <si>
+    <t>0.9024,0.0246,0.0210,0.0006</t>
+  </si>
+  <si>
+    <t>0.9767,0.0009,0.0171,0.0005</t>
+  </si>
+  <si>
+    <t>0.0101,0.0005,0.9905,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0025,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0017,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.4280,0.0049,0.5351,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0035,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9813,0.0166,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0016,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0026,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.6783,0.3978,0.0008</t>
+  </si>
+  <si>
+    <t>0.3073,0.0004,0.8010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0126,0.0003,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0024,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0052,0.9973,0.0022</t>
+  </si>
+  <si>
+    <t>0.9896,0.0005,0.0066,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0000,0.0077,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0002,0.0013,0.0002</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.9911,0.0003,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.1392,0.0001,0.9567,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0970,0.9058,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.5301,0.0025,0.4190,0.0090</t>
-  </si>
-  <si>
-    <t>0.0314,0.0002,0.9779,0.0008</t>
-  </si>
-  <si>
-    <t>0.4263,0.0148,0.3850,0.0008</t>
-  </si>
-  <si>
-    <t>0.9756,0.0005,0.0217,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0018,0.0065,0.9960</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9588,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6660,0.3802,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.8906,0.1220,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.6665,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.3459,0.9914,0.0000</t>
-  </si>
-  <si>
-    <t>0.0065,0.0123,0.9924,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0059,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9720,0.0033,0.0137,0.0009</t>
-  </si>
-  <si>
-    <t>0.0020,0.0006,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.9419,0.0089,0.0143,0.0013</t>
-  </si>
-  <si>
-    <t>0.4839,0.0003,0.0000,0.4369</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9858,0.9800,0.0000</t>
-  </si>
-  <si>
-    <t>0.9955,0.0005,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.0101,0.9882,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9948,0.0002,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.1700,0.8595,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.8433,0.0000,0.0001,0.5421</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.4965,0.0000,0.0127,0.3594</t>
-  </si>
-  <si>
-    <t>0.9937,0.0008,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.0448,0.9436,0.0107,0.0007</t>
-  </si>
-  <si>
-    <t>0.9933,0.0016,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0606,0.9364,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9933,0.0019,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9888,0.0044,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.3035,0.7707,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.4939,0.5798,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.7505,0.3384,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.1906,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.9816,0.0169,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9890,0.0079,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9577,0.0249,0.0055,0.0031</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9497,0.0280,0.0135,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0037,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0441,0.0389,0.8507,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0063,0.9911,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.1829,0.0147,0.7024,0.0145</t>
-  </si>
-  <si>
-    <t>0.1968,0.0016,0.8387,0.0003</t>
-  </si>
-  <si>
-    <t>0.5882,0.1975,0.0274,0.0003</t>
-  </si>
-  <si>
-    <t>0.2119,0.0015,0.8002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0006,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.3315,0.0038,0.6619,0.0057</t>
-  </si>
-  <si>
-    <t>0.0041,0.9947,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0074,0.9912,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.9368,0.0612,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9571,0.0425,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.9953,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9668,0.0059,0.0122,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0004,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.2870,0.0209,0.5229,0.0070</t>
-  </si>
-  <si>
-    <t>0.1319,0.0009,0.9022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.0004,0.9955,0.0008</t>
-  </si>
-  <si>
-    <t>0.0147,0.0063,0.9672,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0113,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.4496,0.0013,0.5800,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0151,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0118,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9956,0.0026,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0016,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0062,0.0460,0.9716,0.0011</t>
-  </si>
-  <si>
-    <t>0.2823,0.0007,0.8004,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0071,0.0002,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0260,0.0006,0.9826,0.0000</t>
-  </si>
-  <si>
-    <t>0.0090,0.0039,0.9846,0.0014</t>
-  </si>
-  <si>
-    <t>0.9442,0.0007,0.0568,0.0004</t>
-  </si>
-  <si>
-    <t>0.9499,0.0002,0.0757,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0001,0.0000</t>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0018,0.0011,0.0002</t>
   </si>
   <si>
     <t>0.9994,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0010,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0193,0.0020,0.9770,0.0000</t>
+    <t>0.9984,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1527,0.0063,0.7526,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0007,0.2635,0.9387,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0336,0.9851,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.4293,0.0004,0.3993,0.0557</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9963,0.0051</t>
-  </si>
-  <si>
-    <t>0.0039,0.0015,0.9889,0.0018</t>
-  </si>
-  <si>
-    <t>0.7954,0.0000,0.0067,0.2188</t>
-  </si>
-  <si>
-    <t>0.0061,0.0125,0.0013,0.9949</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.0035,0.9979</t>
+    <t>0.0013,0.0026,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0268,0.9848,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.3331,0.0012,0.4991,0.0667</t>
+  </si>
+  <si>
+    <t>0.0137,0.0006,0.9832,0.0012</t>
+  </si>
+  <si>
+    <t>0.0221,0.0001,0.9765,0.0009</t>
+  </si>
+  <si>
+    <t>0.6670,0.0000,0.0012,0.5849</t>
+  </si>
+  <si>
+    <t>0.0023,0.0265,0.0013,0.9966</t>
+  </si>
+  <si>
+    <t>0.0039,0.0000,0.0010,0.9983</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.9099,0.0053,0.0010,0.0487</t>
+    <t>0.6691,0.0006,0.0030,0.3516</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1908,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1916,7 +1922,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1930,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1944,7 +1950,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1958,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1972,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1986,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2014,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2028,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2042,7 +2048,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2056,7 +2062,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2070,7 +2076,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2084,7 +2090,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2095,10 +2101,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2112,7 +2118,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2126,7 +2132,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2140,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2154,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2168,7 +2174,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2182,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2196,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2210,7 +2216,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2221,10 +2227,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2238,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2252,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2266,7 +2272,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2280,7 +2286,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2294,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2305,10 +2311,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2322,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2336,7 +2342,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2350,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2364,7 +2370,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2378,7 +2384,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2392,7 +2398,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2406,7 +2412,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2420,7 +2426,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2434,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2448,7 +2454,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2462,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2476,7 +2482,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2490,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2504,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2515,10 +2521,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2532,7 +2538,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2546,7 +2552,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2560,7 +2566,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2574,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2588,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2602,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2616,7 +2622,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2630,7 +2636,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2644,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2658,7 +2664,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2672,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2686,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2700,7 +2706,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2714,7 +2720,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2728,7 +2734,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2742,7 +2748,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2756,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2770,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2784,7 +2790,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2798,7 +2804,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2812,7 +2818,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2826,7 +2832,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2840,7 +2846,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2854,7 +2860,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2868,7 +2874,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2882,7 +2888,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2896,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2907,10 +2913,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2924,7 +2930,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2935,10 +2941,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2952,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2966,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2980,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2994,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3008,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3022,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3036,7 +3042,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3050,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3064,7 +3070,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3078,7 +3084,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3092,7 +3098,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3106,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3120,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3134,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3148,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3162,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3176,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3190,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3232,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3246,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3274,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3509,7 +3515,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>372</v>
@@ -3537,7 +3543,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>374</v>
@@ -3582,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3596,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>281</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3610,7 +3616,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3624,7 +3630,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3736,7 +3742,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>273</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3750,7 +3756,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3764,7 +3770,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3778,7 +3784,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3792,7 +3798,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3806,7 +3812,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3820,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3834,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3848,7 +3854,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3862,7 +3868,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3876,7 +3882,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3887,10 +3893,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3904,7 +3910,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3918,7 +3924,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3932,7 +3938,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3943,10 +3949,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3960,7 +3966,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3974,7 +3980,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3988,7 +3994,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4002,7 +4008,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4016,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4030,7 +4036,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4058,7 +4064,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4072,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4086,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4100,7 +4106,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4114,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4128,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4142,7 +4148,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4156,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4170,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4184,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4198,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4212,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4226,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4240,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4254,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4268,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4282,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4293,10 +4299,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4307,10 +4313,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4321,10 +4327,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4338,7 +4344,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4352,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4366,7 +4372,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4380,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4394,7 +4400,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4408,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4422,7 +4428,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4436,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4450,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4464,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4478,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4492,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4506,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4520,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4534,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4548,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4559,10 +4565,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4576,7 +4582,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4587,10 +4593,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4604,7 +4610,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4618,7 +4624,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4632,7 +4638,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4646,7 +4652,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4660,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4671,10 +4677,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4688,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4702,7 +4708,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4716,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4730,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4744,7 +4750,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4755,10 +4761,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4769,10 +4775,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4786,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4800,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4814,7 +4820,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4828,7 +4834,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4842,7 +4848,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4856,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4870,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4884,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4898,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4912,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>323</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4926,7 +4932,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4940,7 +4946,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4954,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4968,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4979,10 +4985,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4996,7 +5002,7 @@
         <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5010,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5024,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5038,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5052,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>472</v>
+        <v>330</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5066,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5080,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>474</v>
+        <v>330</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5094,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5108,7 +5114,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5122,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5136,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5150,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5164,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5178,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5192,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5206,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5234,7 +5240,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5248,7 +5254,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5262,7 +5268,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5276,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5290,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5304,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5318,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5332,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5343,10 +5349,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5360,7 +5366,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5374,7 +5380,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5385,10 +5391,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5402,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5416,7 +5422,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5430,7 +5436,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5444,7 +5450,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>499</v>
+        <v>398</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5458,7 +5464,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
